--- a/Data/EXCEL/Transfer/salemon/202208/8176-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/8176-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32FD6096-C0DD-44A4-8052-5176056F1382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B1CF81A-4AC2-4DD0-B379-88A726F385C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="8176-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,23 +1227,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q240"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.125" customWidth="1"/>
-    <col min="2" max="5" width="9.5" customWidth="1"/>
-    <col min="6" max="6" width="8.875" customWidth="1"/>
-    <col min="7" max="7" width="10.375" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="10" width="9.5" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="9.5" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="9.625" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="5" width="13.75" customWidth="1"/>
+    <col min="6" max="6" width="13.125" customWidth="1"/>
+    <col min="7" max="7" width="15.125" customWidth="1"/>
+    <col min="8" max="8" width="15.75" customWidth="1"/>
+    <col min="9" max="10" width="13.75" customWidth="1"/>
+    <col min="11" max="11" width="15.75" customWidth="1"/>
+    <col min="12" max="12" width="13.75" customWidth="1"/>
+    <col min="13" max="13" width="15.75" customWidth="1"/>
+    <col min="14" max="15" width="13.75" customWidth="1"/>
+    <col min="16" max="16" width="15.75" customWidth="1"/>
+    <col min="17" max="17" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1262,7 +1270,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1301,7 +1309,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1344,7 +1352,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1383,7 +1391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1436,7 +1444,7 @@
         <v>4.12</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1489,7 +1497,7 @@
         <v>-13.9</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1542,7 +1550,7 @@
         <v>-26.7</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1595,7 +1603,7 @@
         <v>-45.9</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1648,7 +1656,7 @@
         <v>-47.8</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1701,7 +1709,7 @@
         <v>-43</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1754,7 +1762,7 @@
         <v>-65.599999999999994</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1807,7 +1815,7 @@
         <v>-88.1</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1860,7 +1868,7 @@
         <v>-36.9</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1913,7 +1921,7 @@
         <v>-39.200000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1966,7 +1974,7 @@
         <v>-36.799999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2019,7 +2027,7 @@
         <v>-33.799999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2072,7 +2080,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2125,7 +2133,7 @@
         <v>-20.399999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2178,7 +2186,7 @@
         <v>-14.3</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2231,7 +2239,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2284,7 +2292,7 @@
         <v>-8.56</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2337,7 +2345,7 @@
         <v>-2.23</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2390,7 +2398,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2443,7 +2451,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2496,7 +2504,7 @@
         <v>-61.9</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2549,7 +2557,7 @@
         <v>-62</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2602,7 +2610,7 @@
         <v>-64.599999999999994</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2655,7 +2663,7 @@
         <v>-58.4</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2708,7 +2716,7 @@
         <v>-57.4</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2761,7 +2769,7 @@
         <v>-55.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2814,7 +2822,7 @@
         <v>-57.4</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2867,7 +2875,7 @@
         <v>-54.9</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2920,7 +2928,7 @@
         <v>-54.6</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2973,7 +2981,7 @@
         <v>-62.3</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3026,7 +3034,7 @@
         <v>-58.4</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3079,7 +3087,7 @@
         <v>-45.9</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3132,7 +3140,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3185,7 +3193,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3238,7 +3246,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3291,7 +3299,7 @@
         <v>-12.8</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3344,7 +3352,7 @@
         <v>-7.14</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3397,7 +3405,7 @@
         <v>-11.5</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3450,7 +3458,7 @@
         <v>-7.04</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3503,7 +3511,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3556,7 +3564,7 @@
         <v>-7.64</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3609,7 +3617,7 @@
         <v>-14.2</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3662,7 +3670,7 @@
         <v>-8.58</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3715,7 +3723,7 @@
         <v>-12.2</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3768,7 +3776,7 @@
         <v>-20.2</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3821,7 +3829,7 @@
         <v>-15.7</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3874,7 +3882,7 @@
         <v>-14.5</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3927,7 +3935,7 @@
         <v>-12.1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3980,7 +3988,7 @@
         <v>-18.899999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4033,7 +4041,7 @@
         <v>-18.8</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4086,7 +4094,7 @@
         <v>-20.6</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4139,7 +4147,7 @@
         <v>-22.8</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4192,7 +4200,7 @@
         <v>-19.3</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4245,7 +4253,7 @@
         <v>-17.8</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4298,7 +4306,7 @@
         <v>-18.8</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4351,7 +4359,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4404,7 +4412,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4457,7 +4465,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4510,7 +4518,7 @@
         <v>-0.24</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4563,7 +4571,7 @@
         <v>-2.4900000000000002</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4616,7 +4624,7 @@
         <v>-2.4900000000000002</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4669,7 +4677,7 @@
         <v>-7.14</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4722,7 +4730,7 @@
         <v>-10.9</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4775,7 +4783,7 @@
         <v>-10.7</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4828,7 +4836,7 @@
         <v>-13.1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4881,7 +4889,7 @@
         <v>-15.1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4934,7 +4942,7 @@
         <v>-12.8</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4987,7 +4995,7 @@
         <v>-32.9</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5040,7 +5048,7 @@
         <v>-7.58</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5093,7 +5101,7 @@
         <v>-5.14</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5146,7 +5154,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5199,7 +5207,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5252,7 +5260,7 @@
         <v>5.16</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5305,7 +5313,7 @@
         <v>9.83</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5358,7 +5366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5411,7 +5419,7 @@
         <v>8.31</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5464,7 +5472,7 @@
         <v>-3.7</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5517,7 +5525,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5570,7 +5578,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5623,7 +5631,7 @@
         <v>-12.1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5676,7 +5684,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5729,7 +5737,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5782,7 +5790,7 @@
         <v>6.16</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5835,7 +5843,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5888,7 +5896,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5941,7 +5949,7 @@
         <v>-4.55</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5994,7 +6002,7 @@
         <v>-4.09</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6047,7 +6055,7 @@
         <v>-0.18</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6100,7 +6108,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6153,7 +6161,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6206,7 +6214,7 @@
         <v>42.6</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6259,7 +6267,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41974</v>
       </c>
@@ -6312,7 +6320,7 @@
         <v>-30.6</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41944</v>
       </c>
@@ -6365,7 +6373,7 @@
         <v>-31.4</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41913</v>
       </c>
@@ -6418,7 +6426,7 @@
         <v>-30.6</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41883</v>
       </c>
@@ -6471,7 +6479,7 @@
         <v>-31.8</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41852</v>
       </c>
@@ -6524,7 +6532,7 @@
         <v>-35.1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41821</v>
       </c>
@@ -6577,7 +6585,7 @@
         <v>-35.299999999999997</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41791</v>
       </c>
@@ -6630,7 +6638,7 @@
         <v>-37.6</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41760</v>
       </c>
@@ -6683,7 +6691,7 @@
         <v>-36.299999999999997</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41730</v>
       </c>
@@ -6736,7 +6744,7 @@
         <v>-27.2</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41699</v>
       </c>
@@ -6789,7 +6797,7 @@
         <v>-26.2</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41671</v>
       </c>
@@ -6842,7 +6850,7 @@
         <v>-39</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41640</v>
       </c>
@@ -6895,7 +6903,7 @@
         <v>-25.4</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41609</v>
       </c>
@@ -6948,7 +6956,7 @@
         <v>-22.5</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41579</v>
       </c>
@@ -7001,7 +7009,7 @@
         <v>-23</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41548</v>
       </c>
@@ -7054,7 +7062,7 @@
         <v>-23.8</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41518</v>
       </c>
@@ -7107,7 +7115,7 @@
         <v>-20.399999999999999</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41487</v>
       </c>
@@ -7160,7 +7168,7 @@
         <v>-14.1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41456</v>
       </c>
@@ -7213,7 +7221,7 @@
         <v>-8.34</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41426</v>
       </c>
@@ -7266,7 +7274,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41395</v>
       </c>
@@ -7319,7 +7327,7 @@
         <v>5.39</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41365</v>
       </c>
@@ -7372,7 +7380,7 @@
         <v>9.19</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41334</v>
       </c>
@@ -7425,7 +7433,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41306</v>
       </c>
@@ -7478,7 +7486,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41275</v>
       </c>
@@ -7531,7 +7539,7 @@
         <v>68.8</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41244</v>
       </c>
@@ -7584,7 +7592,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41214</v>
       </c>
@@ -7637,7 +7645,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41183</v>
       </c>
@@ -7690,7 +7698,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41153</v>
       </c>
@@ -7743,7 +7751,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>41122</v>
       </c>
@@ -7796,7 +7804,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>41091</v>
       </c>
@@ -7849,7 +7857,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>41061</v>
       </c>
@@ -7902,7 +7910,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>41030</v>
       </c>
@@ -7955,7 +7963,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>41000</v>
       </c>
@@ -8008,7 +8016,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>40969</v>
       </c>
@@ -8061,7 +8069,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="5" customFormat="1">
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>40940</v>
       </c>
@@ -8114,7 +8122,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="5" customFormat="1">
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>40909</v>
       </c>
@@ -8167,7 +8175,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:17" s="5" customFormat="1">
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>40878</v>
       </c>
@@ -8220,7 +8228,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:17" s="5" customFormat="1">
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>40848</v>
       </c>
@@ -8273,7 +8281,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:17" s="5" customFormat="1">
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>40817</v>
       </c>
@@ -8326,7 +8334,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:17" s="5" customFormat="1">
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>40787</v>
       </c>
@@ -8379,7 +8387,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:17" s="5" customFormat="1">
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>40756</v>
       </c>
@@ -8432,7 +8440,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:17" s="5" customFormat="1">
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>40725</v>
       </c>
@@ -8485,7 +8493,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:17" s="5" customFormat="1">
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>40695</v>
       </c>
@@ -8538,7 +8546,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:17" s="5" customFormat="1">
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>40664</v>
       </c>
@@ -8591,7 +8599,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="141" spans="1:17" s="5" customFormat="1">
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>40634</v>
       </c>
@@ -8644,7 +8652,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="142" spans="1:17" s="5" customFormat="1">
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>40603</v>
       </c>
@@ -8697,7 +8705,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:17" s="5" customFormat="1">
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>40575</v>
       </c>
@@ -8750,7 +8758,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" s="5" customFormat="1">
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>40544</v>
       </c>
@@ -8803,7 +8811,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:17" s="5" customFormat="1">
+    <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>40513</v>
       </c>
@@ -8856,7 +8864,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:17" s="5" customFormat="1">
+    <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>40483</v>
       </c>
@@ -8909,7 +8917,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:17" s="5" customFormat="1">
+    <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>40452</v>
       </c>
@@ -8962,7 +8970,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:17" s="5" customFormat="1">
+    <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>40422</v>
       </c>
@@ -9015,7 +9023,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:17" s="5" customFormat="1">
+    <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>40391</v>
       </c>
@@ -9068,7 +9076,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:17" s="5" customFormat="1">
+    <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>40360</v>
       </c>
@@ -9121,7 +9129,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:17" s="5" customFormat="1">
+    <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>40330</v>
       </c>
@@ -9174,7 +9182,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:17" s="5" customFormat="1">
+    <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>40299</v>
       </c>
@@ -9227,7 +9235,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:17" s="5" customFormat="1">
+    <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>40269</v>
       </c>
@@ -9280,7 +9288,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:17" s="5" customFormat="1">
+    <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>40238</v>
       </c>
@@ -9333,7 +9341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:17" s="5" customFormat="1">
+    <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>40210</v>
       </c>
@@ -9386,7 +9394,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:17" s="5" customFormat="1">
+    <row r="156" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>40179</v>
       </c>
@@ -9439,7 +9447,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:17" s="5" customFormat="1">
+    <row r="157" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>40148</v>
       </c>
@@ -9492,7 +9500,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:17" s="5" customFormat="1">
+    <row r="158" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>40118</v>
       </c>
@@ -9545,7 +9553,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:17" s="5" customFormat="1">
+    <row r="159" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>40087</v>
       </c>
@@ -9598,7 +9606,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:17" s="5" customFormat="1">
+    <row r="160" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>40057</v>
       </c>
@@ -9651,7 +9659,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="1:17" s="5" customFormat="1">
+    <row r="161" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
         <v>40026</v>
       </c>
@@ -9704,7 +9712,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:17" s="5" customFormat="1">
+    <row r="162" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
         <v>39995</v>
       </c>
@@ -9757,7 +9765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:17" s="5" customFormat="1">
+    <row r="163" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>39965</v>
       </c>
@@ -9810,7 +9818,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:17" s="5" customFormat="1">
+    <row r="164" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
         <v>39934</v>
       </c>
@@ -9863,7 +9871,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" spans="1:17" s="5" customFormat="1">
+    <row r="165" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
         <v>39904</v>
       </c>
@@ -9916,7 +9924,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:17" s="5" customFormat="1">
+    <row r="166" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
         <v>39873</v>
       </c>
@@ -9969,7 +9977,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:17" s="5" customFormat="1">
+    <row r="167" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>39845</v>
       </c>
@@ -10022,7 +10030,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:17" s="5" customFormat="1">
+    <row r="168" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
         <v>39814</v>
       </c>
@@ -10075,7 +10083,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:17" s="5" customFormat="1">
+    <row r="169" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
         <v>39783</v>
       </c>
@@ -10128,7 +10136,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:17" s="5" customFormat="1">
+    <row r="170" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>39753</v>
       </c>
@@ -10181,7 +10189,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:17" s="5" customFormat="1">
+    <row r="171" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>39722</v>
       </c>
@@ -10234,7 +10242,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:17" s="5" customFormat="1">
+    <row r="172" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>39692</v>
       </c>
@@ -10287,7 +10295,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:17" s="5" customFormat="1">
+    <row r="173" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>39661</v>
       </c>
@@ -10340,7 +10348,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:17" s="5" customFormat="1">
+    <row r="174" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
         <v>39630</v>
       </c>
@@ -10393,7 +10401,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:17" s="5" customFormat="1">
+    <row r="175" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
         <v>39600</v>
       </c>
@@ -10446,7 +10454,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:17" s="5" customFormat="1">
+    <row r="176" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>39569</v>
       </c>
@@ -10499,7 +10507,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:17" s="5" customFormat="1">
+    <row r="177" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>39539</v>
       </c>
@@ -10552,7 +10560,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:17" s="5" customFormat="1">
+    <row r="178" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>39508</v>
       </c>
@@ -10605,7 +10613,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:17" s="5" customFormat="1">
+    <row r="179" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>39479</v>
       </c>
@@ -10658,7 +10666,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:17" s="5" customFormat="1">
+    <row r="180" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>39448</v>
       </c>
@@ -10711,7 +10719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:17" s="5" customFormat="1">
+    <row r="181" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>39417</v>
       </c>
@@ -10764,7 +10772,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:17" s="5" customFormat="1">
+    <row r="182" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>39387</v>
       </c>
@@ -10817,7 +10825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:17" s="5" customFormat="1">
+    <row r="183" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>39356</v>
       </c>
@@ -10870,7 +10878,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:17" s="5" customFormat="1">
+    <row r="184" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>39326</v>
       </c>
@@ -10923,7 +10931,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:17" s="5" customFormat="1">
+    <row r="185" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>39295</v>
       </c>
@@ -10976,7 +10984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:17" s="5" customFormat="1">
+    <row r="186" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
         <v>39264</v>
       </c>
@@ -11029,7 +11037,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:17" s="5" customFormat="1">
+    <row r="187" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
         <v>39234</v>
       </c>
@@ -11082,7 +11090,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:17" s="5" customFormat="1">
+    <row r="188" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
         <v>39203</v>
       </c>
@@ -11135,7 +11143,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="189" spans="1:17" s="5" customFormat="1">
+    <row r="189" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
         <v>39173</v>
       </c>
@@ -11188,7 +11196,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" spans="1:17" s="5" customFormat="1">
+    <row r="190" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
         <v>39142</v>
       </c>
@@ -11241,7 +11249,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="191" spans="1:17" s="5" customFormat="1">
+    <row r="191" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
         <v>39114</v>
       </c>
@@ -11294,7 +11302,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:17" s="5" customFormat="1">
+    <row r="192" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
         <v>39083</v>
       </c>
@@ -11347,7 +11355,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:17" s="5" customFormat="1">
+    <row r="193" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
         <v>39052</v>
       </c>
@@ -11400,7 +11408,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:17" s="5" customFormat="1">
+    <row r="194" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A194" s="6">
         <v>39022</v>
       </c>
@@ -11453,7 +11461,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:17" s="5" customFormat="1">
+    <row r="195" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A195" s="6">
         <v>38991</v>
       </c>
@@ -11506,7 +11514,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="196" spans="1:17" s="5" customFormat="1">
+    <row r="196" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A196" s="6">
         <v>38961</v>
       </c>
@@ -11559,7 +11567,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:17" s="5" customFormat="1">
+    <row r="197" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A197" s="6">
         <v>38930</v>
       </c>
@@ -11612,7 +11620,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:17" s="5" customFormat="1">
+    <row r="198" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
         <v>38899</v>
       </c>
@@ -11665,7 +11673,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:17" s="5" customFormat="1">
+    <row r="199" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A199" s="6">
         <v>38869</v>
       </c>
@@ -11718,7 +11726,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:17" s="5" customFormat="1">
+    <row r="200" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <v>38838</v>
       </c>
@@ -11771,7 +11779,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:17" s="5" customFormat="1">
+    <row r="201" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A201" s="6">
         <v>38808</v>
       </c>
@@ -11824,7 +11832,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:17" s="5" customFormat="1">
+    <row r="202" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A202" s="6">
         <v>38777</v>
       </c>
@@ -11877,7 +11885,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:17" s="5" customFormat="1">
+    <row r="203" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
         <v>38749</v>
       </c>
@@ -11930,7 +11938,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="204" spans="1:17" s="5" customFormat="1">
+    <row r="204" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A204" s="6">
         <v>38718</v>
       </c>
@@ -11983,7 +11991,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:17" s="5" customFormat="1">
+    <row r="205" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
         <v>38687</v>
       </c>
@@ -12036,7 +12044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:17" s="5" customFormat="1">
+    <row r="206" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A206" s="6">
         <v>38657</v>
       </c>
@@ -12089,7 +12097,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:17" s="5" customFormat="1">
+    <row r="207" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A207" s="6">
         <v>38626</v>
       </c>
@@ -12142,7 +12150,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:17" s="5" customFormat="1">
+    <row r="208" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A208" s="6">
         <v>38596</v>
       </c>
@@ -12195,7 +12203,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:17" s="5" customFormat="1">
+    <row r="209" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
         <v>38565</v>
       </c>
@@ -12248,7 +12256,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:17" s="5" customFormat="1">
+    <row r="210" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A210" s="6">
         <v>38534</v>
       </c>
@@ -12301,7 +12309,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:17" s="5" customFormat="1">
+    <row r="211" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A211" s="6">
         <v>38504</v>
       </c>
@@ -12354,7 +12362,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:17" s="5" customFormat="1">
+    <row r="212" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A212" s="6">
         <v>38473</v>
       </c>
@@ -12407,7 +12415,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:17" s="5" customFormat="1">
+    <row r="213" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
         <v>38443</v>
       </c>
@@ -12460,7 +12468,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:17" s="5" customFormat="1">
+    <row r="214" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A214" s="6">
         <v>38412</v>
       </c>
@@ -12513,7 +12521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:17" s="5" customFormat="1">
+    <row r="215" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A215" s="6">
         <v>38384</v>
       </c>
@@ -12566,7 +12574,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:17" s="5" customFormat="1">
+    <row r="216" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>38353</v>
       </c>
@@ -12619,7 +12627,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:17" s="5" customFormat="1">
+    <row r="217" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A217" s="6">
         <v>38322</v>
       </c>
@@ -12672,7 +12680,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:17" s="5" customFormat="1">
+    <row r="218" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A218" s="6">
         <v>38292</v>
       </c>
@@ -12725,7 +12733,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="219" spans="1:17" s="5" customFormat="1">
+    <row r="219" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A219" s="6">
         <v>38261</v>
       </c>
@@ -12778,7 +12786,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:17" s="5" customFormat="1">
+    <row r="220" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>38231</v>
       </c>
@@ -12831,7 +12839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="221" spans="1:17" s="5" customFormat="1">
+    <row r="221" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
         <v>38200</v>
       </c>
@@ -12884,7 +12892,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:17" s="5" customFormat="1">
+    <row r="222" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>38169</v>
       </c>
@@ -12937,7 +12945,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" spans="1:17" s="5" customFormat="1">
+    <row r="223" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A223" s="6">
         <v>38139</v>
       </c>
@@ -12990,7 +12998,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:17" s="5" customFormat="1">
+    <row r="224" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>38108</v>
       </c>
@@ -13043,7 +13051,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" spans="1:17" s="5" customFormat="1">
+    <row r="225" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A225" s="6">
         <v>38078</v>
       </c>
@@ -13096,7 +13104,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:17" s="5" customFormat="1">
+    <row r="226" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>38047</v>
       </c>
@@ -13149,7 +13157,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" spans="1:17" s="5" customFormat="1">
+    <row r="227" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A227" s="6">
         <v>38018</v>
       </c>
@@ -13202,7 +13210,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:17" s="5" customFormat="1">
+    <row r="228" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>37987</v>
       </c>
@@ -13255,7 +13263,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" spans="1:17" s="5" customFormat="1">
+    <row r="229" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A229" s="6">
         <v>37956</v>
       </c>
@@ -13308,7 +13316,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" spans="1:17" s="5" customFormat="1">
+    <row r="230" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>37926</v>
       </c>
@@ -13361,7 +13369,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:17" s="5" customFormat="1">
+    <row r="231" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A231" s="6">
         <v>37895</v>
       </c>
@@ -13414,7 +13422,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" spans="1:17" s="5" customFormat="1">
+    <row r="232" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>37865</v>
       </c>
@@ -13467,7 +13475,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="233" spans="1:17" s="5" customFormat="1">
+    <row r="233" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A233" s="6">
         <v>37834</v>
       </c>
@@ -13520,7 +13528,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:17" s="5" customFormat="1">
+    <row r="234" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>37803</v>
       </c>
@@ -13573,7 +13581,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" spans="1:17" s="5" customFormat="1">
+    <row r="235" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
         <v>37773</v>
       </c>
@@ -13626,7 +13634,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:17" s="5" customFormat="1">
+    <row r="236" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A236" s="6">
         <v>37742</v>
       </c>
@@ -13679,7 +13687,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:17" s="5" customFormat="1">
+    <row r="237" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A237" s="6">
         <v>37712</v>
       </c>
@@ -13732,7 +13740,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="238" spans="1:17" s="5" customFormat="1">
+    <row r="238" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A238" s="6">
         <v>37681</v>
       </c>
@@ -13785,7 +13793,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="239" spans="1:17" s="5" customFormat="1">
+    <row r="239" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
         <v>37653</v>
       </c>
@@ -13838,7 +13846,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:17" s="5" customFormat="1">
+    <row r="240" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A240" s="6">
         <v>37622</v>
       </c>
@@ -13906,7 +13914,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>